--- a/data/WP18_auswertung_sachgebiete.xlsx
+++ b/data/WP18_auswertung_sachgebiete.xlsx
@@ -4154,13 +4154,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{779CF360-E351-4C7F-8AFA-D8866D4C0E1E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{134D0E5B-EC45-42A8-8368-31DED9BBACD2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FF894B5-3D1D-41BE-B374-FD3A088C2F97}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8B0789C-802B-4D18-92E9-780F38491569}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82BCBA1C-ED76-47C8-9F6D-E22930FD9F7B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1089DD27-CD90-4965-B294-BAB24DFE0584}"/>
 </file>